--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/8.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/8.xlsx
@@ -426,13 +426,13 @@
         <v>-9.847732623766642</v>
       </c>
       <c r="E2">
-        <v>-16.8800927216292</v>
+        <v>-11.81236350065145</v>
       </c>
       <c r="F2">
-        <v>-3.097382666118654</v>
+        <v>-3.676835604785742</v>
       </c>
       <c r="G2">
-        <v>-10.92084923505805</v>
+        <v>-3.799157994798421</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.91811316631175</v>
       </c>
       <c r="E3">
-        <v>-17.27025698518207</v>
+        <v>-12.29363613276464</v>
       </c>
       <c r="F3">
-        <v>-3.281182482186614</v>
+        <v>-4.287491486781481</v>
       </c>
       <c r="G3">
-        <v>-10.94922523910413</v>
+        <v>-3.765354850293021</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.1049225246568</v>
       </c>
       <c r="E4">
-        <v>-17.86083339441839</v>
+        <v>-12.00596029295337</v>
       </c>
       <c r="F4">
-        <v>-3.17502222931344</v>
+        <v>-4.088484501932928</v>
       </c>
       <c r="G4">
-        <v>-10.51771835426467</v>
+        <v>-3.678192480787932</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.3943545614229</v>
       </c>
       <c r="E5">
-        <v>-18.40262908164409</v>
+        <v>-13.75838916444164</v>
       </c>
       <c r="F5">
-        <v>-3.137242877173963</v>
+        <v>-3.769736180642303</v>
       </c>
       <c r="G5">
-        <v>-10.79790514444722</v>
+        <v>-4.094500747364039</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.78585141020633</v>
       </c>
       <c r="E6">
-        <v>-18.99373985081331</v>
+        <v>-13.60204359932682</v>
       </c>
       <c r="F6">
-        <v>-3.058409636551743</v>
+        <v>-3.961723580119534</v>
       </c>
       <c r="G6">
-        <v>-10.93644488113009</v>
+        <v>-4.388760696815042</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.25637778902046</v>
       </c>
       <c r="E7">
-        <v>-19.53798091400315</v>
+        <v>-13.32713805621719</v>
       </c>
       <c r="F7">
-        <v>-3.183576779482151</v>
+        <v>-4.399233279214718</v>
       </c>
       <c r="G7">
-        <v>-11.05803054601532</v>
+        <v>-3.499536529319286</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.78284936085164</v>
       </c>
       <c r="E8">
-        <v>-20.09671762249154</v>
+        <v>-15.35803637985914</v>
       </c>
       <c r="F8">
-        <v>-2.841501632128692</v>
+        <v>-3.785250673729335</v>
       </c>
       <c r="G8">
-        <v>-10.61331346317754</v>
+        <v>-4.550465857707596</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.34381808817481</v>
       </c>
       <c r="E9">
-        <v>-20.40070049720443</v>
+        <v>-16.56647325422799</v>
       </c>
       <c r="F9">
-        <v>-2.870971630850688</v>
+        <v>-3.737143236811754</v>
       </c>
       <c r="G9">
-        <v>-10.63153736771869</v>
+        <v>-4.158770034048883</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.9015204590608</v>
       </c>
       <c r="E10">
-        <v>-22.10820237806261</v>
+        <v>-16.63493472427595</v>
       </c>
       <c r="F10">
-        <v>-2.47069373304173</v>
+        <v>-3.195689996013288</v>
       </c>
       <c r="G10">
-        <v>-10.41750328539611</v>
+        <v>-5.04296408889401</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.42026403372597</v>
       </c>
       <c r="E11">
-        <v>-21.88866648664476</v>
+        <v>-16.65434829234684</v>
       </c>
       <c r="F11">
-        <v>-2.625832036972827</v>
+        <v>-3.309832397179838</v>
       </c>
       <c r="G11">
-        <v>-10.37583177159116</v>
+        <v>-4.655950568400625</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.87328705269059</v>
       </c>
       <c r="E12">
-        <v>-22.27563817602221</v>
+        <v>-15.35025646151396</v>
       </c>
       <c r="F12">
-        <v>-2.666900007701418</v>
+        <v>-2.933079305242983</v>
       </c>
       <c r="G12">
-        <v>-10.17617600214207</v>
+        <v>-5.113260979583554</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.22601053058265</v>
       </c>
       <c r="E13">
-        <v>-22.34571631129091</v>
+        <v>-17.3296116940006</v>
       </c>
       <c r="F13">
-        <v>-2.640461833673669</v>
+        <v>-2.555464711207217</v>
       </c>
       <c r="G13">
-        <v>-9.478007522388104</v>
+        <v>-4.863871734957958</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.45771210840745</v>
       </c>
       <c r="E14">
-        <v>-24.00968144303935</v>
+        <v>-19.20735702670314</v>
       </c>
       <c r="F14">
-        <v>-2.409966947109901</v>
+        <v>-2.615556139341099</v>
       </c>
       <c r="G14">
-        <v>-9.026327687401182</v>
+        <v>-4.160108772445136</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.55943277356247</v>
       </c>
       <c r="E15">
-        <v>-24.67331572344142</v>
+        <v>-19.50568836585445</v>
       </c>
       <c r="F15">
-        <v>-2.000625881546914</v>
+        <v>-2.920224699886341</v>
       </c>
       <c r="G15">
-        <v>-8.480319295023344</v>
+        <v>-4.258801354510115</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.52034641862277</v>
       </c>
       <c r="E16">
-        <v>-25.50555867657107</v>
+        <v>-19.94610057699643</v>
       </c>
       <c r="F16">
-        <v>-2.120110424094118</v>
+        <v>-2.294408037684565</v>
       </c>
       <c r="G16">
-        <v>-8.240770433854522</v>
+        <v>-5.003546774300401</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.3477485141527</v>
       </c>
       <c r="E17">
-        <v>-26.21898805716148</v>
+        <v>-20.03814633967633</v>
       </c>
       <c r="F17">
-        <v>-1.938626723284385</v>
+        <v>-2.042760789490311</v>
       </c>
       <c r="G17">
-        <v>-7.94550643060633</v>
+        <v>-3.99215288448184</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.05676780990528</v>
       </c>
       <c r="E18">
-        <v>-26.83801234011399</v>
+        <v>-21.94101564617343</v>
       </c>
       <c r="F18">
-        <v>-1.771850685711358</v>
+        <v>-1.322758753590231</v>
       </c>
       <c r="G18">
-        <v>-7.27500192982004</v>
+        <v>-2.923829800606913</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.65724476885808</v>
       </c>
       <c r="E19">
-        <v>-27.447295875476</v>
+        <v>-20.97745600376934</v>
       </c>
       <c r="F19">
-        <v>-1.775301664311421</v>
+        <v>-1.308897681839187</v>
       </c>
       <c r="G19">
-        <v>-6.747181348546204</v>
+        <v>-4.349960251874608</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.17105579083691</v>
       </c>
       <c r="E20">
-        <v>-27.90047385484559</v>
+        <v>-22.54611940002636</v>
       </c>
       <c r="F20">
-        <v>-1.419226279483248</v>
+        <v>-0.7376563492360507</v>
       </c>
       <c r="G20">
-        <v>-6.691686048311316</v>
+        <v>-3.389559826311377</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.6165316154693</v>
       </c>
       <c r="E21">
-        <v>-29.20116480169871</v>
+        <v>-25.185526889975</v>
       </c>
       <c r="F21">
-        <v>-1.138651613215833</v>
+        <v>-1.36854261994296</v>
       </c>
       <c r="G21">
-        <v>-6.287186898127649</v>
+        <v>-3.048430908105267</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.00409852167119</v>
       </c>
       <c r="E22">
-        <v>-29.99247261403604</v>
+        <v>-24.6802759879912</v>
       </c>
       <c r="F22">
-        <v>-1.186273626835373</v>
+        <v>-0.1462359867007185</v>
       </c>
       <c r="G22">
-        <v>-5.987447308672374</v>
+        <v>-1.173376847960584</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.35832411741286</v>
       </c>
       <c r="E23">
-        <v>-29.73205139503993</v>
+        <v>-25.16161201874049</v>
       </c>
       <c r="F23">
-        <v>-1.020372345239702</v>
+        <v>0.05297974673334023</v>
       </c>
       <c r="G23">
-        <v>-5.798104418584617</v>
+        <v>-1.999283283023735</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.69844264284479</v>
       </c>
       <c r="E24">
-        <v>-30.71485931621362</v>
+        <v>-26.76116866467783</v>
       </c>
       <c r="F24">
-        <v>-0.8846426895561977</v>
+        <v>0.116372218967378</v>
       </c>
       <c r="G24">
-        <v>-5.473627699792688</v>
+        <v>-1.999496562425099</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.03784020253078</v>
       </c>
       <c r="E25">
-        <v>-30.48935036757965</v>
+        <v>-27.01858524116984</v>
       </c>
       <c r="F25">
-        <v>-0.7835694409036161</v>
+        <v>-0.2782305337650001</v>
       </c>
       <c r="G25">
-        <v>-5.623992958975802</v>
+        <v>-1.934689155404506</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.402410677851446</v>
       </c>
       <c r="E26">
-        <v>-30.82508010932331</v>
+        <v>-27.07073514784218</v>
       </c>
       <c r="F26">
-        <v>-0.5232964029440115</v>
+        <v>-0.2218742142503413</v>
       </c>
       <c r="G26">
-        <v>-5.328164585619385</v>
+        <v>-0.6237427057595593</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.806933575619567</v>
       </c>
       <c r="E27">
-        <v>-31.73231459201999</v>
+        <v>-26.82665492730276</v>
       </c>
       <c r="F27">
-        <v>-0.7641881287803161</v>
+        <v>0.3360477988831817</v>
       </c>
       <c r="G27">
-        <v>-5.501518083047968</v>
+        <v>-2.415322489431968</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.258058202009513</v>
       </c>
       <c r="E28">
-        <v>-31.74583208693289</v>
+        <v>-26.90209930427054</v>
       </c>
       <c r="F28">
-        <v>-0.7446411431764561</v>
+        <v>0.8673775616520349</v>
       </c>
       <c r="G28">
-        <v>-5.634177870696319</v>
+        <v>-2.136005222962678</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.769177771676527</v>
       </c>
       <c r="E29">
-        <v>-31.68294290415136</v>
+        <v>-27.65315577539069</v>
       </c>
       <c r="F29">
-        <v>-0.6573602117804862</v>
+        <v>-0.3154192599462811</v>
       </c>
       <c r="G29">
-        <v>-5.584943141196851</v>
+        <v>-0.3614385730759892</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.337847720119317</v>
       </c>
       <c r="E30">
-        <v>-31.73733214122049</v>
+        <v>-26.80221022460935</v>
       </c>
       <c r="F30">
-        <v>-0.8050266417383317</v>
+        <v>0.01669891122552748</v>
       </c>
       <c r="G30">
-        <v>-5.728263617691836</v>
+        <v>-1.10254839937841</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.953709150825475</v>
       </c>
       <c r="E31">
-        <v>-31.24929396893985</v>
+        <v>-27.31998688569836</v>
       </c>
       <c r="F31">
-        <v>-0.5519537732438603</v>
+        <v>-0.2619903908331158</v>
       </c>
       <c r="G31">
-        <v>-6.443921008357645</v>
+        <v>-2.049666440069009</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.614108251440006</v>
       </c>
       <c r="E32">
-        <v>-30.51818089734948</v>
+        <v>-26.98031963580503</v>
       </c>
       <c r="F32">
-        <v>-0.7423540207773267</v>
+        <v>-0.3348055422739979</v>
       </c>
       <c r="G32">
-        <v>-5.887219114917576</v>
+        <v>-2.634511370824435</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.306887716080674</v>
       </c>
       <c r="E33">
-        <v>-30.45691290826271</v>
+        <v>-27.87736505198445</v>
       </c>
       <c r="F33">
-        <v>-0.5650717994345933</v>
+        <v>0.1962326351690699</v>
       </c>
       <c r="G33">
-        <v>-6.154632109569201</v>
+        <v>-2.385151657192874</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.019672162698013</v>
       </c>
       <c r="E34">
-        <v>-30.1249916131595</v>
+        <v>-26.75393216321358</v>
       </c>
       <c r="F34">
-        <v>-0.6147026040059229</v>
+        <v>0.3921572649118062</v>
       </c>
       <c r="G34">
-        <v>-6.163970466127381</v>
+        <v>-1.746727659593275</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.750220264496679</v>
       </c>
       <c r="E35">
-        <v>-29.77392845842586</v>
+        <v>-26.60685638439246</v>
       </c>
       <c r="F35">
-        <v>-0.5067870406062173</v>
+        <v>-0.3087981192957047</v>
       </c>
       <c r="G35">
-        <v>-6.482275207165994</v>
+        <v>-2.492270416222507</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.491121383004937</v>
       </c>
       <c r="E36">
-        <v>-30.12129411413223</v>
+        <v>-26.82825347862746</v>
       </c>
       <c r="F36">
-        <v>-0.4422174582928014</v>
+        <v>0.01983096837551241</v>
       </c>
       <c r="G36">
-        <v>-6.782044327615304</v>
+        <v>-2.55872499646594</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.236733996287715</v>
       </c>
       <c r="E37">
-        <v>-29.49548844135324</v>
+        <v>-25.79577046182663</v>
       </c>
       <c r="F37">
-        <v>-0.483799845178531</v>
+        <v>-0.05246479670381444</v>
       </c>
       <c r="G37">
-        <v>-6.455365909156988</v>
+        <v>-1.649544439445642</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.989574504968835</v>
       </c>
       <c r="E38">
-        <v>-29.31211241488664</v>
+        <v>-24.52565577147331</v>
       </c>
       <c r="F38">
-        <v>-0.4449104807193026</v>
+        <v>-0.1361299043865645</v>
       </c>
       <c r="G38">
-        <v>-6.986139589834325</v>
+        <v>-2.780227139057815</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.748826341379544</v>
       </c>
       <c r="E39">
-        <v>-28.08578353971347</v>
+        <v>-25.24942818669724</v>
       </c>
       <c r="F39">
-        <v>-0.5739576965644236</v>
+        <v>0.4097368779340173</v>
       </c>
       <c r="G39">
-        <v>-7.233688069165072</v>
+        <v>-2.341327662044931</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.515548862305693</v>
       </c>
       <c r="E40">
-        <v>-27.86686804923467</v>
+        <v>-24.83352407688477</v>
       </c>
       <c r="F40">
-        <v>-0.5839950243841452</v>
+        <v>0.1312074507841143</v>
       </c>
       <c r="G40">
-        <v>-7.36500255597405</v>
+        <v>-2.201216220235082</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.298004623518491</v>
       </c>
       <c r="E41">
-        <v>-27.14531911474851</v>
+        <v>-23.32916501153668</v>
       </c>
       <c r="F41">
-        <v>-0.1867994816810047</v>
+        <v>0.2930795533325685</v>
       </c>
       <c r="G41">
-        <v>-7.043154095651236</v>
+        <v>-3.160110565102527</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.103824768479489</v>
       </c>
       <c r="E42">
-        <v>-27.12822412536955</v>
+        <v>-22.16425582932955</v>
       </c>
       <c r="F42">
-        <v>-0.2529760967558516</v>
+        <v>-0.08655211532901409</v>
       </c>
       <c r="G42">
-        <v>-7.059061457771424</v>
+        <v>-1.350382344984829</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.941552995340915</v>
       </c>
       <c r="E43">
-        <v>-26.21392975169492</v>
+        <v>-22.41469402737575</v>
       </c>
       <c r="F43">
-        <v>-0.5142050706982869</v>
+        <v>0.08700825127294112</v>
       </c>
       <c r="G43">
-        <v>-7.011818429758539</v>
+        <v>-1.831422550485662</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.823765200402043</v>
       </c>
       <c r="E44">
-        <v>-25.65471755343572</v>
+        <v>-22.35049385136901</v>
       </c>
       <c r="F44">
-        <v>-0.3367820268970775</v>
+        <v>0.6307494428379394</v>
       </c>
       <c r="G44">
-        <v>-7.115688779444321</v>
+        <v>-2.357723926177476</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.760943677407711</v>
       </c>
       <c r="E45">
-        <v>-25.00143083614118</v>
+        <v>-21.49371562606579</v>
       </c>
       <c r="F45">
-        <v>-0.3282167079521306</v>
+        <v>0.3369573462914555</v>
       </c>
       <c r="G45">
-        <v>-7.289616490645807</v>
+        <v>-2.364440586709659</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.759665850416277</v>
       </c>
       <c r="E46">
-        <v>-24.5799068900852</v>
+        <v>-20.5888993484892</v>
       </c>
       <c r="F46">
-        <v>-0.244876320291278</v>
+        <v>0.03482524673358627</v>
       </c>
       <c r="G46">
-        <v>-6.919895007770696</v>
+        <v>-2.490085122663916</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.826150129109648</v>
       </c>
       <c r="E47">
-        <v>-23.85083616027229</v>
+        <v>-19.55825036366149</v>
       </c>
       <c r="F47">
-        <v>-0.215120534815317</v>
+        <v>0.2918444575349945</v>
       </c>
       <c r="G47">
-        <v>-7.669473666918043</v>
+        <v>-1.776232403855802</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.962444925450299</v>
       </c>
       <c r="E48">
-        <v>-23.50308558427527</v>
+        <v>-19.19514826077846</v>
       </c>
       <c r="F48">
-        <v>-0.2433181612066121</v>
+        <v>0.1978968252812941</v>
       </c>
       <c r="G48">
-        <v>-7.610549490153535</v>
+        <v>-1.779018160959771</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.163409501718633</v>
       </c>
       <c r="E49">
-        <v>-22.21070438722623</v>
+        <v>-18.39957236168891</v>
       </c>
       <c r="F49">
-        <v>-0.2336618823921783</v>
+        <v>0.07542684661440123</v>
       </c>
       <c r="G49">
-        <v>-7.384286295078906</v>
+        <v>-1.489591450865831</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.423127853581721</v>
       </c>
       <c r="E50">
-        <v>-22.07947826743196</v>
+        <v>-17.72430443156114</v>
       </c>
       <c r="F50">
-        <v>-0.1177807380471527</v>
+        <v>0.1772083493963765</v>
       </c>
       <c r="G50">
-        <v>-7.065597651117838</v>
+        <v>-2.49396352654718</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.73388338716592</v>
       </c>
       <c r="E51">
-        <v>-21.95452408413831</v>
+        <v>-17.84047790375391</v>
       </c>
       <c r="F51">
-        <v>-0.1793276077077531</v>
+        <v>0.360575757680075</v>
       </c>
       <c r="G51">
-        <v>-7.603809861070435</v>
+        <v>-2.335693804627364</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.081829226582936</v>
       </c>
       <c r="E52">
-        <v>-20.83962736887189</v>
+        <v>-18.32757415344096</v>
       </c>
       <c r="F52">
-        <v>-0.04577738666101403</v>
+        <v>0.4776257284304508</v>
       </c>
       <c r="G52">
-        <v>-7.330362699970991</v>
+        <v>-1.379237407378586</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.455402992086788</v>
       </c>
       <c r="E53">
-        <v>-20.72827219302328</v>
+        <v>-16.69685707785684</v>
       </c>
       <c r="F53">
-        <v>0.08792939582485416</v>
+        <v>0.6764728383702637</v>
       </c>
       <c r="G53">
-        <v>-7.437842393372162</v>
+        <v>-1.923460815228087</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.845154300103392</v>
       </c>
       <c r="E54">
-        <v>-19.47303806825915</v>
+        <v>-14.43220798288696</v>
       </c>
       <c r="F54">
-        <v>-0.03380167911874158</v>
+        <v>1.117851013236522</v>
       </c>
       <c r="G54">
-        <v>-7.645123721725404</v>
+        <v>-3.300294193786684</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.237715537235502</v>
       </c>
       <c r="E55">
-        <v>-19.78134110717536</v>
+        <v>-16.7225788102204</v>
       </c>
       <c r="F55">
-        <v>-0.1645487048744071</v>
+        <v>0.7765006873605124</v>
       </c>
       <c r="G55">
-        <v>-8.486327211698686</v>
+        <v>-2.046588654246249</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.625241586281295</v>
       </c>
       <c r="E56">
-        <v>-18.84142462756532</v>
+        <v>-14.08293131114936</v>
       </c>
       <c r="F56">
-        <v>-0.3265815106990044</v>
+        <v>0.8963455697279337</v>
       </c>
       <c r="G56">
-        <v>-8.230050683019817</v>
+        <v>-1.566306410925648</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.003876908787845</v>
       </c>
       <c r="E57">
-        <v>-18.69284086689965</v>
+        <v>-14.40174946671137</v>
       </c>
       <c r="F57">
-        <v>-0.1323699447452575</v>
+        <v>0.4140385898567551</v>
       </c>
       <c r="G57">
-        <v>-7.956127744794252</v>
+        <v>-3.242994221694101</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.365791302916645</v>
       </c>
       <c r="E58">
-        <v>-16.96884175523153</v>
+        <v>-13.39189976300088</v>
       </c>
       <c r="F58">
-        <v>-0.2743040722757304</v>
+        <v>0.3834188171796742</v>
       </c>
       <c r="G58">
-        <v>-8.246837412517936</v>
+        <v>-2.805709105688463</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.709444095162936</v>
       </c>
       <c r="E59">
-        <v>-17.29198007499686</v>
+        <v>-12.52516795182881</v>
       </c>
       <c r="F59">
-        <v>-0.293150259056822</v>
+        <v>0.4855399505967973</v>
       </c>
       <c r="G59">
-        <v>-8.222674496954184</v>
+        <v>-3.314446102372569</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.035986944724966</v>
       </c>
       <c r="E60">
-        <v>-17.02536163932126</v>
+        <v>-12.91433142262597</v>
       </c>
       <c r="F60">
-        <v>-0.3010296897922509</v>
+        <v>0.1501538700209446</v>
       </c>
       <c r="G60">
-        <v>-8.665265348221444</v>
+        <v>-2.33731472807773</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.341021866071211</v>
       </c>
       <c r="E61">
-        <v>-16.72760994484293</v>
+        <v>-13.24813429867937</v>
       </c>
       <c r="F61">
-        <v>-0.5421011713549631</v>
+        <v>0.3612392799697174</v>
       </c>
       <c r="G61">
-        <v>-8.762396068824128</v>
+        <v>-3.326268343651248</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.625797041127784</v>
       </c>
       <c r="E62">
-        <v>-16.25246886653613</v>
+        <v>-12.16735963506075</v>
       </c>
       <c r="F62">
-        <v>-0.7157128967358918</v>
+        <v>0.339913789552047</v>
       </c>
       <c r="G62">
-        <v>-8.889195594767308</v>
+        <v>-2.252682180394972</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.891482197534183</v>
       </c>
       <c r="E63">
-        <v>-16.39282891840388</v>
+        <v>-12.28745023727016</v>
       </c>
       <c r="F63">
-        <v>-0.5974725620276932</v>
+        <v>-0.005208921476311044</v>
       </c>
       <c r="G63">
-        <v>-9.457217702587462</v>
+        <v>-4.518362385969989</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.13345484617383</v>
       </c>
       <c r="E64">
-        <v>-15.7561118875034</v>
+        <v>-12.18312325308145</v>
       </c>
       <c r="F64">
-        <v>-0.6395817905816032</v>
+        <v>0.7330163689179552</v>
       </c>
       <c r="G64">
-        <v>-9.40605033358948</v>
+        <v>-4.066456146695465</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.353021560418791</v>
       </c>
       <c r="E65">
-        <v>-15.70052939753325</v>
+        <v>-10.67730149062888</v>
       </c>
       <c r="F65">
-        <v>-0.6757764758795248</v>
+        <v>0.1020514033077801</v>
       </c>
       <c r="G65">
-        <v>-9.294393645143137</v>
+        <v>-4.684700631704479</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.55016554179867</v>
       </c>
       <c r="E66">
-        <v>-16.15141596905497</v>
+        <v>-11.77251292938395</v>
       </c>
       <c r="F66">
-        <v>-0.9194308070041658</v>
+        <v>-0.001657710420509563</v>
       </c>
       <c r="G66">
-        <v>-9.305316831714528</v>
+        <v>-4.383018559086014</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.720515004186723</v>
       </c>
       <c r="E67">
-        <v>-15.12244251961009</v>
+        <v>-12.15663620861058</v>
       </c>
       <c r="F67">
-        <v>-1.09253225806497</v>
+        <v>-0.501251889620711</v>
       </c>
       <c r="G67">
-        <v>-9.2004227409022</v>
+        <v>-5.740617416863145</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.866112958705441</v>
       </c>
       <c r="E68">
-        <v>-14.95582637544587</v>
+        <v>-10.38418242506039</v>
       </c>
       <c r="F68">
-        <v>-1.040294581277031</v>
+        <v>0.06679774337943878</v>
       </c>
       <c r="G68">
-        <v>-9.512896751229679</v>
+        <v>-4.160824078745096</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.985759866970866</v>
       </c>
       <c r="E69">
-        <v>-14.41422994107651</v>
+        <v>-12.09191525809296</v>
       </c>
       <c r="F69">
-        <v>-1.122136452306219</v>
+        <v>-0.199948985833044</v>
       </c>
       <c r="G69">
-        <v>-9.552740624626017</v>
+        <v>-4.001737332656978</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.07503395024201</v>
       </c>
       <c r="E70">
-        <v>-13.85761708689772</v>
+        <v>-10.56097857879385</v>
       </c>
       <c r="F70">
-        <v>-1.223082132378769</v>
+        <v>-0.435265799048508</v>
       </c>
       <c r="G70">
-        <v>-9.331743790154295</v>
+        <v>-4.750905839109396</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.13621069215477</v>
       </c>
       <c r="E71">
-        <v>-15.17491394793696</v>
+        <v>-12.41710950505778</v>
       </c>
       <c r="F71">
-        <v>-1.469776571871685</v>
+        <v>-0.07232324845112699</v>
       </c>
       <c r="G71">
-        <v>-9.433271347646635</v>
+        <v>-4.71536364717749</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.16744113143592</v>
       </c>
       <c r="E72">
-        <v>-14.5209660734373</v>
+        <v>-9.360878625073113</v>
       </c>
       <c r="F72">
-        <v>-1.50990186049589</v>
+        <v>-0.1549048515710153</v>
       </c>
       <c r="G72">
-        <v>-8.814872645224327</v>
+        <v>-5.968731220897301</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.16621738862603</v>
       </c>
       <c r="E73">
-        <v>-14.38554658671193</v>
+        <v>-10.1380553342695</v>
       </c>
       <c r="F73">
-        <v>-1.454339116953113</v>
+        <v>-0.6826809181818587</v>
       </c>
       <c r="G73">
-        <v>-8.666728773036956</v>
+        <v>-5.29965405148937</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.1364912399828</v>
       </c>
       <c r="E74">
-        <v>-14.97122318707195</v>
+        <v>-11.98907814185277</v>
       </c>
       <c r="F74">
-        <v>-1.726688923278132</v>
+        <v>-0.5591042406648257</v>
       </c>
       <c r="G74">
-        <v>-8.865482206557202</v>
+        <v>-4.276743073997158</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.07716812613879</v>
       </c>
       <c r="E75">
-        <v>-15.36943907741045</v>
+        <v>-11.67703458340623</v>
       </c>
       <c r="F75">
-        <v>-1.923849477185845</v>
+        <v>-0.6662833854434425</v>
       </c>
       <c r="G75">
-        <v>-8.856760719652197</v>
+        <v>-4.262348355015875</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.988416752650629</v>
       </c>
       <c r="E76">
-        <v>-15.32931679770249</v>
+        <v>-11.41548803861922</v>
       </c>
       <c r="F76">
-        <v>-2.006441020714567</v>
+        <v>-0.9608003034673759</v>
       </c>
       <c r="G76">
-        <v>-8.218218598076458</v>
+        <v>-4.916348311358157</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.876510407716101</v>
       </c>
       <c r="E77">
-        <v>-15.33099233308533</v>
+        <v>-11.87031438252761</v>
       </c>
       <c r="F77">
-        <v>-2.022801276919857</v>
+        <v>-1.165737570552571</v>
       </c>
       <c r="G77">
-        <v>-7.946648295709017</v>
+        <v>-5.045894219746594</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.741449661995814</v>
       </c>
       <c r="E78">
-        <v>-15.91895128434522</v>
+        <v>-11.21759372448403</v>
       </c>
       <c r="F78">
-        <v>-2.035119928566888</v>
+        <v>-1.906583815409295</v>
       </c>
       <c r="G78">
-        <v>-7.905190061305433</v>
+        <v>-5.548679080521867</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.585622709845588</v>
       </c>
       <c r="E79">
-        <v>-16.15184164561169</v>
+        <v>-11.00528527758242</v>
       </c>
       <c r="F79">
-        <v>-1.949384730744542</v>
+        <v>-1.287393264062512</v>
       </c>
       <c r="G79">
-        <v>-7.629541200539601</v>
+        <v>-3.628593535695365</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.415830403158756</v>
       </c>
       <c r="E80">
-        <v>-16.83984817312304</v>
+        <v>-12.71436759586927</v>
       </c>
       <c r="F80">
-        <v>-2.166426102319444</v>
+        <v>-1.587596924306664</v>
       </c>
       <c r="G80">
-        <v>-7.022029591251531</v>
+        <v>-2.462532705229259</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.231377712364965</v>
       </c>
       <c r="E81">
-        <v>-16.76688087143745</v>
+        <v>-12.01609954625654</v>
       </c>
       <c r="F81">
-        <v>-2.15434353538221</v>
+        <v>-1.407137085606792</v>
       </c>
       <c r="G81">
-        <v>-7.16598334350749</v>
+        <v>-1.986266677097418</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.03454017203269</v>
       </c>
       <c r="E82">
-        <v>-17.57270017873235</v>
+        <v>-13.91346222836031</v>
       </c>
       <c r="F82">
-        <v>-2.143732148952348</v>
+        <v>-2.096823359666618</v>
       </c>
       <c r="G82">
-        <v>-6.308452495054411</v>
+        <v>-3.21103184248355</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.830833192596486</v>
       </c>
       <c r="E83">
-        <v>-19.18007749928093</v>
+        <v>-14.36034562885924</v>
       </c>
       <c r="F83">
-        <v>-2.150268796127839</v>
+        <v>-2.02817572462922</v>
       </c>
       <c r="G83">
-        <v>-6.121915049399978</v>
+        <v>-3.353328577851989</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.617855304808533</v>
       </c>
       <c r="E84">
-        <v>-19.53072629864286</v>
+        <v>-15.84722478453773</v>
       </c>
       <c r="F84">
-        <v>-2.384032420463054</v>
+        <v>-1.512097862480711</v>
       </c>
       <c r="G84">
-        <v>-6.665551118590338</v>
+        <v>-4.156627396370566</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.397514827780466</v>
       </c>
       <c r="E85">
-        <v>-20.79326938045537</v>
+        <v>-16.72816241867186</v>
       </c>
       <c r="F85">
-        <v>-2.429532156796622</v>
+        <v>-1.821852598879142</v>
       </c>
       <c r="G85">
-        <v>-5.804164834804912</v>
+        <v>-2.399339659215913</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.176252106094447</v>
       </c>
       <c r="E86">
-        <v>-21.65458060824026</v>
+        <v>-17.83623472360872</v>
       </c>
       <c r="F86">
-        <v>-2.336810508299065</v>
+        <v>-1.853653623472615</v>
       </c>
       <c r="G86">
-        <v>-5.950714033314391</v>
+        <v>-3.112916755413034</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.954418600725206</v>
       </c>
       <c r="E87">
-        <v>-22.56633903647061</v>
+        <v>-20.56409236787519</v>
       </c>
       <c r="F87">
-        <v>-2.623763603568037</v>
+        <v>-1.49766356048693</v>
       </c>
       <c r="G87">
-        <v>-5.202795672276122</v>
+        <v>-0.7672928677637061</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.737946763482648</v>
       </c>
       <c r="E88">
-        <v>-23.86755528630861</v>
+        <v>-20.48841703873301</v>
       </c>
       <c r="F88">
-        <v>-2.677792210680829</v>
+        <v>-2.25606125387417</v>
       </c>
       <c r="G88">
-        <v>-5.466428699691267</v>
+        <v>-2.05444717988112</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.538258706083192</v>
       </c>
       <c r="E89">
-        <v>-25.22645070958232</v>
+        <v>-22.09826237761577</v>
       </c>
       <c r="F89">
-        <v>-2.838269342522969</v>
+        <v>-2.034992359986857</v>
       </c>
       <c r="G89">
-        <v>-5.706994739543515</v>
+        <v>-1.262406232532998</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.360492850481261</v>
       </c>
       <c r="E90">
-        <v>-26.90039206956965</v>
+        <v>-23.37727099092017</v>
       </c>
       <c r="F90">
-        <v>-2.521060127866745</v>
+        <v>-2.334143165262051</v>
       </c>
       <c r="G90">
-        <v>-4.765218527551693</v>
+        <v>-1.551882160950329</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.213221121349219</v>
       </c>
       <c r="E91">
-        <v>-28.19206229619949</v>
+        <v>-26.72032635760266</v>
       </c>
       <c r="F91">
-        <v>-2.821551231599669</v>
+        <v>-2.325205080985844</v>
       </c>
       <c r="G91">
-        <v>-4.938706555064214</v>
+        <v>-0.8643907761507942</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.110047799086054</v>
       </c>
       <c r="E92">
-        <v>-29.31971572274551</v>
+        <v>-27.28478705723674</v>
       </c>
       <c r="F92">
-        <v>-3.007740887624705</v>
+        <v>-2.029032256523715</v>
       </c>
       <c r="G92">
-        <v>-5.336571075254683</v>
+        <v>-1.308861767371616</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.055828890568717</v>
       </c>
       <c r="E93">
-        <v>-31.4980543673662</v>
+        <v>-26.80829196520165</v>
       </c>
       <c r="F93">
-        <v>-3.025513510251769</v>
+        <v>-2.627772073430183</v>
       </c>
       <c r="G93">
-        <v>-5.237789900207599</v>
+        <v>-0.5695992688071619</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.055405573246918</v>
       </c>
       <c r="E94">
-        <v>-32.99074808367053</v>
+        <v>-30.68959948819883</v>
       </c>
       <c r="F94">
-        <v>-3.165212702529489</v>
+        <v>-2.372918215019693</v>
       </c>
       <c r="G94">
-        <v>-5.046064843267685</v>
+        <v>-1.28727132951047</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.116351331548194</v>
       </c>
       <c r="E95">
-        <v>-34.53758876368458</v>
+        <v>-31.3437262374218</v>
       </c>
       <c r="F95">
-        <v>-3.264461057793703</v>
+        <v>-2.026055104078053</v>
       </c>
       <c r="G95">
-        <v>-6.09939602583751</v>
+        <v>-0.8841010740583786</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.236198058995323</v>
       </c>
       <c r="E96">
-        <v>-36.62277216949348</v>
+        <v>-33.138623138154</v>
       </c>
       <c r="F96">
-        <v>-3.449901041319206</v>
+        <v>-3.05062960990465</v>
       </c>
       <c r="G96">
-        <v>-5.921626004189913</v>
+        <v>-0.912621451853072</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.405165311306792</v>
       </c>
       <c r="E97">
-        <v>-38.85689934965166</v>
+        <v>-38.10910564405404</v>
       </c>
       <c r="F97">
-        <v>-3.528485771720587</v>
+        <v>-3.382457852485479</v>
       </c>
       <c r="G97">
-        <v>-6.453928734113951</v>
+        <v>-1.124453834509263</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.625019809863803</v>
       </c>
       <c r="E98">
-        <v>-40.08048623381318</v>
+        <v>-38.52421727091516</v>
       </c>
       <c r="F98">
-        <v>-3.420790554050026</v>
+        <v>-3.023606608490524</v>
       </c>
       <c r="G98">
-        <v>-5.9253731592108</v>
+        <v>-1.49556327410402</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.872241512237764</v>
       </c>
       <c r="E99">
-        <v>-42.21419223861426</v>
+        <v>-40.13292143434799</v>
       </c>
       <c r="F99">
-        <v>-3.524348076543603</v>
+        <v>-3.628927804412235</v>
       </c>
       <c r="G99">
-        <v>-6.795497336009027</v>
+        <v>-1.063334520521487</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.146485749549536</v>
       </c>
       <c r="E100">
-        <v>-45.09693275089106</v>
+        <v>-41.35211117024806</v>
       </c>
       <c r="F100">
-        <v>-3.858450187645117</v>
+        <v>-3.866488664921883</v>
       </c>
       <c r="G100">
-        <v>-7.260502211748854</v>
+        <v>-2.190407876418271</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.417578178534017</v>
       </c>
       <c r="E101">
-        <v>-46.64811397324146</v>
+        <v>-45.29044576642384</v>
       </c>
       <c r="F101">
-        <v>-3.728022911706931</v>
+        <v>-3.678643930826053</v>
       </c>
       <c r="G101">
-        <v>-7.488064770561023</v>
+        <v>-2.203230890272581</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.707720071756745</v>
       </c>
       <c r="E102">
-        <v>-49.27101404331365</v>
+        <v>-46.09914971166162</v>
       </c>
       <c r="F102">
-        <v>-4.060672066383935</v>
+        <v>-3.56750104802504</v>
       </c>
       <c r="G102">
-        <v>-7.56218756558888</v>
+        <v>-2.29317573566008</v>
       </c>
     </row>
   </sheetData>
